--- a/public/brdp-template-4-1.xlsx
+++ b/public/brdp-template-4-1.xlsx
@@ -469,22 +469,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRDP-EXT-00027</t>
+          <t>BRDP-EXT-00036</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The root element of an interchanged data module must be element /dmodule/</t>
+          <t>Issue 001 of a data module must have the issue type new</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The root element of an interchanged data module must be element /dmodule/. (S1000D Chap 1.4.2, Para 2.3.1.3)</t>
+          <t>The first issue of a data module (issue number 001) must have the issue type new.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Per S1000D 4.1's own default BREX (Chap 1.4.2, Para 2.3.1.3): The root element of an interchanged data module must be element /dmodule/.</t>
+          <t>Issue 001 of a data module shall have the issue type new.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -500,8 +500,9 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>&lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="2"&gt;//dmodule&lt;/objectPath&gt;
-                  &lt;objectUse&gt;The root element of an interchanged data module must be element /dmodule/ (Chap 1.4.2, Para 2.3.1.3). &lt;/objectUse&gt;
+                  &lt;objectPath allowedObjectFlag="2"&gt;//dmodule[child::identAndStatusSection[child::dmAddress[child::dmIdent[child::issueInfo[attribute::issueNumber = "001"]]]]]/identAndStatusSection/dmStatus/@issueType&lt;/objectPath&gt;
+                  &lt;objectUse&gt;Issue 001 of a data module must have the issue type new. &lt;/objectUse&gt;
+                  &lt;objectValue valueForm="single" valueAllowed="new"&gt;Issue type new&lt;/objectValue&gt;
                &lt;/structureObjectRule&gt;</t>
         </is>
       </c>
@@ -580,7 +581,7 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>&lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="2"&gt;//*/changeInline&lt;/objectPath&gt;
+                  &lt;objectPath allowedObjectFlag="0"&gt;//changeInline[* and not(text()[normalize-space()])]&lt;/objectPath&gt;
                   &lt;objectUse&gt;The element /changeInline/ must not be used to indicate that a complete element has been inserted (or modified) (Chap 3.9.5.2.1.1, Para 2.4.2). &lt;/objectUse&gt;
                &lt;/structureObjectRule&gt;</t>
         </is>
@@ -620,7 +621,7 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>&lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="2"&gt;//internalRef&lt;/objectPath&gt;
+                  &lt;objectPath allowedObjectFlag="0"&gt;//internalRef[attribute::internalRefId = //*[attribute::changeType = "delete"]/attribute::id]&lt;/objectPath&gt;
                   &lt;objectUse&gt;There must be no cross-references to deleted information in the data module (Chap 3.9.5.2.1.1, Para 2.4.1). &lt;/objectUse&gt;
                &lt;/structureObjectRule&gt;</t>
         </is>
@@ -629,22 +630,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRDP-EXT-00044</t>
+          <t>BRDP-EXT-00014</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Editorial changes must not be marked</t>
+          <t>No change markers must appear in a data module if the issue type is not changed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Editorial changes must not be marked. (S1000D Chap 3.9.5.2.1.1, Para 2.1.1)</t>
+          <t>No change markers must appear in a data module if the issue type is not changed. (S1000D Chap 3.9.5.2.1.1, Para 2.1.1)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Per S1000D 4.1's own default BREX (Chap 3.9.5.2.1.1, Para 2.1.1): Editorial changes must not be marked.</t>
+          <t>Per S1000D 4.1's own default BREX (Chap 3.9.5.2.1.1, Para 2.1.1): No change markers must appear in a data module if the issue type is not changed.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -660,8 +661,8 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>&lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="2"&gt;//@changeMark&lt;/objectPath&gt;
-                  &lt;objectUse&gt;Editorial changes must not be marked (Chap 3.9.5.2.1.1, Para 2.1.1). &lt;/objectUse&gt;
+                  &lt;objectPath allowedObjectFlag="0"&gt;//*[attribute::changeMark = "1" and ancestor::dmodule[child::identAndStatusSection[child::dmStatus[attribute::issueType != "changed" and attribute::issueType != "rinstate-changed"]]]]&lt;/objectPath&gt;
+                  &lt;objectUse&gt;No change markers must appear in a data module if the issue type is not changed (Chap 3.9.5.2.1.1, Para 2.1.1). &lt;/objectUse&gt;
                &lt;/structureObjectRule&gt;</t>
         </is>
       </c>
@@ -790,7 +791,7 @@
           <t>&lt;contextRules rulesContext="http://www.s1000d.org/S1000D_4-1/xml_schema_flat/update.xsd"&gt;
         &lt;structureObjectRuleGroup&gt;
           &lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="0"&gt;//updateCode[attribute::infoCode="00N"] and (//zoneSpec or //partSpec or //circuitBreakerSpec or //functionalItemSpec or //accessPointSpec or //enterpriseSpec or //supplySpec or //supplyRqmtSpec or //functionalPhysicalAreaSpec or //controlIndicatorSpec or //applicSpec or //warningSpec or //cautionSpec or //zoneIdent or //partIdent or //functionalItemIdent or //circuitBreakerIdent or //accessPointIdent or //enterpriseIdent or //supplyIdent or //supplyRqmtIdent or //functionalPhysicalAreaIdent or //controlIndicatorIdent or //applicSpecIdent or //warningIdent or //cautionIdent)&lt;/objectPath&gt;
+                  &lt;objectPath allowedObjectFlag="0"&gt;/*[descendant::updateCode[attribute::infoCode = "00N"]]//*[self::zoneSpec or self::partSpec or self::circuitBreakerSpec or self::functionalItemSpec or self::accessPointSpec or self::enterpriseSpec or self::supplySpec or self::supplyRqmtSpec or self::functionalPhysicalAreaSpec or self::controlIndicatorSpec or self::applicSpec or self::warningSpec or self::cautionSpec or self::zoneIdent or self::partIdent or self::functionalItemIdent or self::circuitBreakerIdent or self::accessPointIdent or self::enterpriseIdent or self::supplyIdent or self::supplyRqmtIdent or self::functionalPhysicalAreaIdent or self::controlIndicatorIdent or self::applicSpecIdent or self::warningIdent or self::cautionIdent]&lt;/objectPath&gt;
                   &lt;objectUse&gt;Only toolSpec, toolIdent, figure, figureIdent, multimedia, multimediaIdent, applicIdent, applicRefIdent, applic, applicRef elements can be used in the Data update file representing the tool CIR (Chap 4.13.2.1, Para 2.3.1). &lt;/objectUse&gt;
                &lt;/structureObjectRule&gt;
         &lt;/structureObjectRuleGroup&gt;

--- a/public/brdp-template-4-1.xlsx
+++ b/public/brdp-template-4-1.xlsx
@@ -469,22 +469,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRDP-EXT-00036</t>
+          <t>BRDP-S1-00133</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Issue 001 of a data module must have the issue type new</t>
+          <t>Use of the element &lt;parameter&gt;</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The first issue of a data module (issue number 001) must have the issue type new.</t>
+          <t>Decide whether to use the element &lt;parameter&gt; and how to use it. If used, specify the attributes to be used within the project.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Issue 001 of a data module shall have the issue type new.</t>
+          <t>Shall not be used</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -500,32 +500,31 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>&lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="2"&gt;//dmodule[child::identAndStatusSection[child::dmAddress[child::dmIdent[child::issueInfo[attribute::issueNumber = "001"]]]]]/identAndStatusSection/dmStatus/@issueType&lt;/objectPath&gt;
-                  &lt;objectUse&gt;Issue 001 of a data module must have the issue type new. &lt;/objectUse&gt;
-                  &lt;objectValue valueForm="single" valueAllowed="new"&gt;Issue type new&lt;/objectValue&gt;
-               &lt;/structureObjectRule&gt;</t>
+            &lt;objectPath allowedObjectFlag="0"&gt;//parameter&lt;/objectPath&gt;
+            &lt;objectUse&gt;BRDP-S1-00133. The element &amp;lt;parameter&amp;gt; must not be used. &lt;/objectUse&gt;
+          &lt;/structureObjectRule&gt;</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRDP-EXT-00037</t>
+          <t>BRDP-S1-00095</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RFU must not be used on Issue 001 of a data module, unless it is in work</t>
+          <t>Use of the element &lt;internalRef&gt; in titles</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RFU must not be used on Issue 001 of a data module, unless it is in work. (S1000D Chap 3.9.5.2.1.1, Para 2.1.1)</t>
+          <t>Use of the element &lt;internalRef&gt; in titles is strongly discouraged. However, decide whether to use cross-references in titles.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Per S1000D 4.1's own default BREX (Chap 3.9.5.2.1.1, Para 2.1.1): RFU must not be used on Issue 001 of a data module, unless it is in work.</t>
+          <t>The element &lt;internalRef&gt; shall not be used</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -541,31 +540,31 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>&lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="0"&gt;//identAndStatusSection/dmAddress/dmIdent/issueInfo[attribute::issueNumber = "001" and attribute::inWork = "00" and ancestor::dmodule[child::identAndStatusSection[child::dmStatus[child::reasonForUpdate]]]]&lt;/objectPath&gt;
-                  &lt;objectUse&gt;RFU must not be used on Issue 001 of a data module, unless it is in work (Chap 3.9.5.2.1.1, Para 2.1.1). &lt;/objectUse&gt;
-               &lt;/structureObjectRule&gt;</t>
+  &lt;objectPath allowedObjectFlag="0"&gt;//title/internalRef&lt;/objectPath&gt;
+  &lt;objectUse&gt;BRDP-S1-00095. The element &amp;lt;internalRef&amp;gt; must not be used within titles.&lt;/objectUse&gt;
+&lt;/structureObjectRule&gt;</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRDP-EXT-00040</t>
+          <t>BRDP-S1-00150</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The element /changeInline/ must not be used to indicate that a complete element has been...</t>
+          <t>Use of the attribute id on the element &lt;supportEquipDescr&gt; in the element &lt;preliminaryRqmts&gt;</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The element /changeInline/ must not be used to indicate that a complete element has been inserted (or modified). (S1000D Chap 3.9.5.2.1.1, Para 2.4.2)</t>
+          <t>Decide whether to use the attribute id to create cross-references from the procedure to the support equipment listed in Preliminary requirements. The attribute id on element &lt;supportEquipDescr&gt; is used to establish the link between the two and will guarantee consistent use of identification throughout the procedure. The use of cross-references is encouraged.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Per S1000D 4.1's own default BREX (Chap 3.9.5.2.1.1, Para 2.4.2): The element /changeInline/ must not be used to indicate that a complete element has been inserted (or modified).</t>
+          <t>Use of the attribute id on the element &lt;supportEquipDescr&gt; in the element &lt;preliminaryRqmts&gt; is required.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -581,31 +580,31 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>&lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="0"&gt;//changeInline[* and not(text()[normalize-space()])]&lt;/objectPath&gt;
-                  &lt;objectUse&gt;The element /changeInline/ must not be used to indicate that a complete element has been inserted (or modified) (Chap 3.9.5.2.1.1, Para 2.4.2). &lt;/objectUse&gt;
-               &lt;/structureObjectRule&gt;</t>
+  &lt;objectPath allowedObjectFlag="0"&gt;//supportEquipDescr[not(@id)]&lt;/objectPath&gt;
+  &lt;objectUse&gt;BRDP-S1-00150. Every &amp;lt;supportEquipDescr&amp;gt; in Preliminary Requirements must carry an id attribute, to allow cross-referencing from the procedure to the listed support equipment.&lt;/objectUse&gt;
+&lt;/structureObjectRule&gt;</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRDP-EXT-00041</t>
+          <t>BRDP-S1-00338</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>There must be no cross-references to deleted information in the data module</t>
+          <t>Number of characters in assembly code</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>There must be no cross-references to deleted information in the data module. (S1000D Chap 3.9.5.2.1.1, Para 2.4.1)</t>
+          <t>Decide whether to use two or four characters for unit or assembly.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Per S1000D 4.1's own default BREX (Chap 3.9.5.2.1.1, Para 2.4.1): There must be no cross-references to deleted information in the data module.</t>
+          <t>Two characters to be used</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -621,31 +620,31 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>&lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="0"&gt;//internalRef[attribute::internalRefId = //*[attribute::changeType = "delete"]/attribute::id]&lt;/objectPath&gt;
-                  &lt;objectUse&gt;There must be no cross-references to deleted information in the data module (Chap 3.9.5.2.1.1, Para 2.4.1). &lt;/objectUse&gt;
-               &lt;/structureObjectRule&gt;</t>
+            &lt;objectPath allowedObjectFlag="0"&gt;//@assyCode[string-length(.) != 2]&lt;/objectPath&gt;
+            &lt;objectUse&gt;BRDP-S1-00338. The assembly code (@assyCode) must be exactly two characters. &lt;/objectUse&gt;
+          &lt;/structureObjectRule&gt;</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRDP-EXT-00014</t>
+          <t>BRDP-S1-00334</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>No change markers must appear in a data module if the issue type is not changed</t>
+          <t>Allocation of system difference code</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No change markers must appear in a data module if the issue type is not changed. (S1000D Chap 3.9.5.2.1.1, Para 2.1.1)</t>
+          <t>Decide which system difference code values to be used for the Product.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Per S1000D 4.1's own default BREX (Chap 3.9.5.2.1.1, Para 2.1.1): No change markers must appear in a data module if the issue type is not changed.</t>
+          <t>No need for SDC seen, use default. SDC to be used if different LRUs are in identical SNS.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -661,31 +660,33 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>&lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="0"&gt;//*[attribute::changeMark = "1" and ancestor::dmodule[child::identAndStatusSection[child::dmStatus[attribute::issueType != "changed" and attribute::issueType != "rinstate-changed"]]]]&lt;/objectPath&gt;
-                  &lt;objectUse&gt;No change markers must appear in a data module if the issue type is not changed (Chap 3.9.5.2.1.1, Para 2.1.1). &lt;/objectUse&gt;
-               &lt;/structureObjectRule&gt;</t>
+  &lt;objectPath allowedObjectFlag="2"&gt;//@systemDiffCode&lt;/objectPath&gt;
+  &lt;objectUse&gt;BRDP-S1-00334. The system difference code (@systemDiffCode) should be 'A', used only when different LRUs share an identical SNS; no UOC is used.&lt;/objectUse&gt;
+  &lt;objectValue valueForm="single" valueAllowed="A"&gt;SDC to be used if different LRUs are in identical SNS. No UOC is used.&lt;/objectValue&gt;
+  &lt;objectValue valueForm="single" valueAllowed="F"&gt;Only the S1000D and ATA BREX data modules use systemDiffCode F.&lt;/objectValue&gt;
+&lt;/structureObjectRule&gt;</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BRDP-EXT-00007</t>
+          <t>BRDP-S1-00316</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The element answer must not be used in a CSL</t>
+          <t>Use of the element &lt;applic&gt; in the data module status and content</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The element answer must not be used in a CSL. (S1000D Chap 4.5, Para 4.2.6)</t>
+          <t>Decide how to use the element &lt;applic&gt; and to populate its child elements and attributes across the project.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Per S1000D 4.1's own default BREX (Chap 4.5, Para 4.2.6): The element answer must not be used in a CSL.</t>
+          <t>Use &lt;applic&gt; element</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -700,36 +701,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>&lt;contextRules rulesContext="http://www.s1000d.org/S1000D_4-1/xml_schema_flat/dml.xsd"&gt;
-        &lt;structureObjectRuleGroup&gt;
-          &lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="0"&gt;//dml[descendant-or-self::dmlIdent[child::dmlCode[attribute::dmlType="s"]] and descendant-or-self::dmlEntry[child::answer]]&lt;/objectPath&gt;
-                  &lt;objectUse&gt;The element answer must not be used in a CSL (Chap 4.5, Para 4.2.6). &lt;/objectUse&gt;
-               &lt;/structureObjectRule&gt;
-        &lt;/structureObjectRuleGroup&gt;
-      &lt;/contextRules&gt;</t>
+          <t>&lt;structureObjectRule&gt;
+  &lt;objectPath allowedObjectFlag="0"&gt;//dmStatus/applicRef | //pmStatus/applicRef&lt;/objectPath&gt;
+  &lt;objectUse&gt;BRDP-S1-00316. Data module and publication module status must use the &amp;lt;applic&amp;gt; element directly, not &amp;lt;applicRef&amp;gt;.&lt;/objectUse&gt;
+&lt;/structureObjectRule&gt;</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BRDP-EXT-00013</t>
+          <t>BRDP-S1-00187</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>No change markers must appear in a publication module if the issue type is not changed</t>
+          <t>Decide on the minimum number of substeps in a step</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No change markers must appear in a publication module if the issue type is not changed. (S1000D Chap 3.9.5.2.1.1, Para 2.1.1)</t>
+          <t>Decide whether to allow for a single substep, or to insist on a minimum of two substeps in a step.
+Note
+The Schema allows for a single substep.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Per S1000D 4.1's own default BREX (Chap 3.9.5.2.1.1, Para 2.1.1): No change markers must appear in a publication module if the issue type is not changed.</t>
+          <t>A minimum of two sub-steps is required</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -744,36 +743,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>&lt;contextRules rulesContext="http://www.s1000d.org/S1000D_4-1/xml_schema_flat/pm.xsd"&gt;
-        &lt;structureObjectRuleGroup&gt;
-          &lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="0"&gt;//*[attribute::changeMark = "1" and ancestor::pm[child::identAndStatusSection[child::pmStatus[attribute::issueType != "changed" and attribute::issueType != "rinstate-changed"]]]]&lt;/objectPath&gt;
-                  &lt;objectUse&gt;No change markers must appear in a publication module if the issue type is not changed (Chap 3.9.5.2.1.1, Para 2.1.1). &lt;/objectUse&gt;
-               &lt;/structureObjectRule&gt;
-        &lt;/structureObjectRuleGroup&gt;
-      &lt;/contextRules&gt;</t>
+          <t>&lt;structureObjectRule&gt;
+            &lt;objectPath allowedObjectFlag="0"&gt;//proceduralStep[count(proceduralStep) = 1]&lt;/objectPath&gt;
+            &lt;objectUse&gt;BRDP-S1-00187. A &amp;lt;proceduralStep&amp;gt; that has substeps must have at least two -- a single substep is not allowed. &lt;/objectUse&gt;
+          &lt;/structureObjectRule&gt;</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BRDP-EXT-00019</t>
+          <t>BRDP-S1-00120</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Only toolSpec, toolIdent, figure</t>
+          <t>Use of titles for the elements &lt;levelledPara&gt; and &lt;proceduralStep&gt; from sublevel six thru eight for legacy data</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Only toolSpec, toolIdent, figure, figureIdent, multimedia, multimediaIdent, applicIdent, applicRefIdent, applic, applicRef elements can be used in the Data update file representing the tool CIR. (S1000D Chap 4.13.2.1, Para 2.3.1)</t>
+          <t>Decide whether titles can be included for the elements &lt;levelledPara&gt; and &lt;proceduralStep&gt; from sublevel six thru eight when converting legacy data to S1000D.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Per S1000D 4.1's own default BREX (Chap 4.13.2.1, Para 2.3.1): Only toolSpec, toolIdent, figure, figureIdent, multimedia, multimediaIdent, applicIdent, applicRefIdent, applic, applicRef elements can be used in the Data update file representing the tool CIR.</t>
+          <t>There will be a maximum of five levels, while the fifth level must not have a title.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -788,36 +783,41 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>&lt;contextRules rulesContext="http://www.s1000d.org/S1000D_4-1/xml_schema_flat/update.xsd"&gt;
-        &lt;structureObjectRuleGroup&gt;
-          &lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="0"&gt;/*[descendant::updateCode[attribute::infoCode = "00N"]]//*[self::zoneSpec or self::partSpec or self::circuitBreakerSpec or self::functionalItemSpec or self::accessPointSpec or self::enterpriseSpec or self::supplySpec or self::supplyRqmtSpec or self::functionalPhysicalAreaSpec or self::controlIndicatorSpec or self::applicSpec or self::warningSpec or self::cautionSpec or self::zoneIdent or self::partIdent or self::functionalItemIdent or self::circuitBreakerIdent or self::accessPointIdent or self::enterpriseIdent or self::supplyIdent or self::supplyRqmtIdent or self::functionalPhysicalAreaIdent or self::controlIndicatorIdent or self::applicSpecIdent or self::warningIdent or self::cautionIdent]&lt;/objectPath&gt;
-                  &lt;objectUse&gt;Only toolSpec, toolIdent, figure, figureIdent, multimedia, multimediaIdent, applicIdent, applicRefIdent, applic, applicRef elements can be used in the Data update file representing the tool CIR (Chap 4.13.2.1, Para 2.3.1). &lt;/objectUse&gt;
-               &lt;/structureObjectRule&gt;
-        &lt;/structureObjectRuleGroup&gt;
-      &lt;/contextRules&gt;</t>
+          <t>&lt;structureObjectRule&gt;
+  &lt;objectPath allowedObjectFlag="0"&gt;//proceduralStep[count(ancestor-or-self::proceduralStep) &amp;gt; 5] | //levelledPara[count(ancestor-or-self::levelledPara) &amp;gt; 5]&lt;/objectPath&gt;
+  &lt;objectUse&gt;BRDP-S1-00120. A maximum of five levels of &amp;lt;proceduralStep&amp;gt; and &amp;lt;levelledPara&amp;gt; is allowed.&lt;/objectUse&gt;
+&lt;/structureObjectRule&gt;
+&lt;structureObjectRule&gt;
+  &lt;objectPath allowedObjectFlag="0"&gt;//proceduralStep[count(ancestor-or-self::proceduralStep) = 5]/title | //levelledPara[count(ancestor-or-self::levelledPara) = 5]/title&lt;/objectPath&gt;
+  &lt;objectUse&gt;BRDP-S1-00120. A &amp;lt;proceduralStep&amp;gt; or &amp;lt;levelledPara&amp;gt; at level five must not have a &amp;lt;title&amp;gt;.&lt;/objectUse&gt;
+&lt;/structureObjectRule&gt;
+&lt;nonContextRule&gt;
+  &lt;simplePara&gt;BRDP-S1-00120. Decide whether titles can be included for the elements &amp;lt;levelledPara&amp;gt; and &amp;lt;proceduralStep&amp;gt; from sublevel six thru eight when converting legacy data to S1000D.&lt;/simplePara&gt;
+  &lt;simplePara&gt;Decision made by Project. There will be a maximum of five levels, while the fifth level must not have a title.&lt;/simplePara&gt;
+&lt;/nonContextRule&gt;</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BRDP-EXT-00001</t>
+          <t>BRDP-S1-00507</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A DMRL must not contain comments or other data management lists</t>
+          <t>Prefixes to be used for random lists at presentation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A DMRL must not contain comments or other data management lists. (S1000D Chap 4.5, Para 2.1)</t>
+          <t>Decide whether to use a consistent set of prefixes for random list throughout the project.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Per S1000D 4.1's own default BREX (Chap 4.5, Para 2.1): A DMRL must not contain comments or other data management lists.</t>
+          <t>The default prefix (pf02) shall be used/presented.
+Nested randomList should be avoided. The listItemPrefix attribute shall always be the default value, which is pf02.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -832,36 +832,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>&lt;contextRules rulesContext="http://www.s1000d.org/S1000D_4-1/xml_schema_flat/dml.xsd"&gt;
-        &lt;structureObjectRuleGroup&gt;
-          &lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="0"&gt;//dml[(descendant-or-self::dmlIdent[child::dmlCode[attribute::dmlType!="s"]]) and ((descendant-or-self::dmlEntry[child::dmlRef]) or (descendant-or-self::dmlEntry[child::commentRef]))]&lt;/objectPath&gt;
-                  &lt;objectUse&gt;A DMRL must not contain comments or other data management lists (Chap 4.5, Para 2.1). &lt;/objectUse&gt;
-               &lt;/structureObjectRule&gt;
-        &lt;/structureObjectRuleGroup&gt;
-      &lt;/contextRules&gt;</t>
+          <t>&lt;structureObjectRule&gt;
+            &lt;objectPath allowedObjectFlag="0"&gt;//randomList//randomList&lt;/objectPath&gt;
+            &lt;objectUse&gt;BRDP-S1-00507. A &amp;lt;randomList&amp;gt; must not be nested inside another &amp;lt;randomList&amp;gt; -- the default prefix pf02 is always used, without nesting. &lt;/objectUse&gt;
+          &lt;/structureObjectRule&gt;
+&lt;structureObjectRule&gt;
+            &lt;objectPath allowedObjectFlag="0"&gt;//randomList[@listItemPrefix != 'pf02']&lt;/objectPath&gt;
+            &lt;objectUse&gt;BRDP-S1-00507. The attribute listItemPrefix of a &amp;lt;randomList&amp;gt; must be pf02, the default prefix (a &amp;lt;randomList&amp;gt; without the attribute uses pf02). &lt;/objectUse&gt;
+          &lt;/structureObjectRule&gt;
+&lt;nonContextRule&gt;
+          &lt;simplePara&gt;BRDP-S1-00507. Decide whether to use a consistent set of prefixes for random list throughout the project. &lt;/simplePara&gt;
+          &lt;simplePara&gt;Decision made by Project. Nested randomList should be avoided. The listItemPrefix attribute shall always be the default value, which is pf02.&lt;/simplePara&gt;
+        &lt;/nonContextRule&gt;</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BRDP-EXT-00012</t>
+          <t>BRDP-S1-00219</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The entity control number given in a DDN must not include the prefix ICN-</t>
+          <t>Use of the element &lt;partSegment&gt; in the element &lt;itemSeqNumber&gt;</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The entity control number given in a DDN must not include the prefix ICN-. (S1000D Chap 4.4, Para 1)</t>
+          <t>Decide whether to use the element &lt;partSegment&gt; to store the part data in the IPD data module each time the part is listed or whether to store the part data once externally in the part CIR data module.
+Note
+The element &lt;partSegment&gt; must be used for S2000M IPD data modules.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Per S1000D 4.1's own default BREX (Chap 4.4, Para 1): The entity control number given in a DDN must not include the prefix ICN-.</t>
+          <t>&lt;partSegment&gt; shall be used.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -876,14 +882,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>&lt;contextRules rulesContext="http://www.s1000d.org/S1000D_4-1/xml_schema_flat/ddn.xsd"&gt;
-        &lt;structureObjectRuleGroup&gt;
-          &lt;structureObjectRule&gt;
-                  &lt;objectPath allowedObjectFlag="0"&gt;//ddn[descendant-or-self::entityControlNumber[contains((.),"ICN-")]]&lt;/objectPath&gt;
-                  &lt;objectUse&gt;The entity control number given in a DDN must not include the prefix ICN- (Chap 4.4, Para 1). &lt;/objectUse&gt;
-               &lt;/structureObjectRule&gt;
-        &lt;/structureObjectRuleGroup&gt;
-      &lt;/contextRules&gt;</t>
+          <t>&lt;contextRules rulesContext="http://www.s1000d.org/S1000D_4-1/xml_schema_flat/ipd.xsd"&gt;
+  &lt;structureObjectRuleGroup&gt;
+    &lt;structureObjectRule&gt;
+      &lt;objectPath allowedObjectFlag="0"&gt;//itemSeqNumber[not(partSegment)]&lt;/objectPath&gt;
+      &lt;objectUse&gt;BRDP-S1-00219. Every &amp;lt;itemSeqNumber&amp;gt; must contain &amp;lt;partSegment&amp;gt; to store the part data in IPD data modules.&lt;/objectUse&gt;
+    &lt;/structureObjectRule&gt;
+  &lt;/structureObjectRuleGroup&gt;
+&lt;/contextRules&gt;</t>
         </is>
       </c>
     </row>

--- a/public/brdp-template-4-1.xlsx
+++ b/public/brdp-template-4-1.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>No need for SDC seen, use default. SDC to be used if different LRUs are in identical SNS.</t>
+          <t>No need for SDC seen, use default A.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -661,9 +661,8 @@
         <is>
           <t>&lt;structureObjectRule&gt;
   &lt;objectPath allowedObjectFlag="2"&gt;//@systemDiffCode&lt;/objectPath&gt;
-  &lt;objectUse&gt;BRDP-S1-00334. The system difference code (@systemDiffCode) should be 'A', used only when different LRUs share an identical SNS; no UOC is used.&lt;/objectUse&gt;
+  &lt;objectUse&gt;BRDP-S1-00334. The system difference code (@systemDiffCode) must be 'A'; no UOC is used.&lt;/objectUse&gt;
   &lt;objectValue valueForm="single" valueAllowed="A"&gt;SDC to be used if different LRUs are in identical SNS. No UOC is used.&lt;/objectValue&gt;
-  &lt;objectValue valueForm="single" valueAllowed="F"&gt;Only the S1000D and ATA BREX data modules use systemDiffCode F.&lt;/objectValue&gt;
 &lt;/structureObjectRule&gt;</t>
         </is>
       </c>

--- a/public/brdp-template-4-1.xlsx
+++ b/public/brdp-template-4-1.xlsx
@@ -859,7 +859,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Decide whether to use the element &lt;partSegment&gt; to store the part data in the IPD data module each time the part is listed or whether to store the part data once externally in the part CIR data module.
+          <t>Decide whether to use the element &lt;partSegment&gt; to store the part data in the IPD data module each time the part is listed or whether to store the part data once externally in the part CIR data module. 
 Note
 The element &lt;partSegment&gt; must be used for S2000M IPD data modules.</t>
         </is>
